--- a/Farm/Assets/Configs/item.xlsx
+++ b/Farm/Assets/Configs/item.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>#item.xlsx</t>
   </si>
@@ -61,6 +61,9 @@
     <t>使用参数</t>
   </si>
   <si>
+    <t>售价</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -89,6 +92,9 @@
   </si>
   <si>
     <t>use_arg</t>
+  </si>
+  <si>
+    <t>sell_price</t>
   </si>
   <si>
     <t>牧草</t>
@@ -1029,8 +1035,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="12.4444444444444" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.6666666666667" style="1" customWidth="1"/>
@@ -1038,22 +1044,22 @@
     <col min="5" max="5" width="12.4444444444444" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1075,68 +1081,80 @@
       <c r="G6" t="s">
         <v>9</v>
       </c>
+      <c r="H6" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
         <v>11</v>
       </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
       <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
         <v>11</v>
       </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G8" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="H8" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>10000</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="H9">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
